--- a/exemple-ePrescription/ig/StructureDefinition-fr-cda-dicom-serie-imagerie.xlsx
+++ b/exemple-ePrescription/ig/StructureDefinition-fr-cda-dicom-serie-imagerie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T08:51:06+00:00</t>
+    <t>2026-05-06T11:50:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4083,7 +4083,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>156</v>
       </c>
@@ -4102,7 +4102,7 @@
         <v>81</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>74</v>
@@ -4388,7 +4388,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>164</v>
       </c>
@@ -4403,13 +4403,13 @@
         <v>62</v>
       </c>
       <c r="F30" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>74</v>
@@ -4491,7 +4491,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>168</v>
       </c>
@@ -4506,13 +4506,13 @@
         <v>169</v>
       </c>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>74</v>
@@ -4800,7 +4800,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>182</v>
       </c>
@@ -4821,7 +4821,7 @@
         <v>75</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>74</v>
